--- a/data/data_preparation/auriculares/df_alt_cleaned.xlsx
+++ b/data/data_preparation/auriculares/df_alt_cleaned.xlsx
@@ -540,7 +540,7 @@
         <v>9716495</v>
       </c>
       <c r="B2" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>16141900</v>
       </c>
       <c r="B3" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         <v>15397854</v>
       </c>
       <c r="B4" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>16224063</v>
       </c>
       <c r="B5" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>17327007</v>
       </c>
       <c r="B6" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>15289414</v>
       </c>
       <c r="B7" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>6344841</v>
       </c>
       <c r="B8" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>18592787</v>
       </c>
       <c r="B9" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>15466444</v>
       </c>
       <c r="B10" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>15306525</v>
       </c>
       <c r="B11" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>16269805</v>
       </c>
       <c r="B12" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>15285466</v>
       </c>
       <c r="B13" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>18622695</v>
       </c>
       <c r="B14" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>17771463</v>
       </c>
       <c r="B15" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>13997252</v>
       </c>
       <c r="B16" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>15283838</v>
       </c>
       <c r="B17" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>15248885</v>
       </c>
       <c r="B18" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>18155224</v>
       </c>
       <c r="B19" t="n">
-        <v>25535.5</v>
+        <v>32268.7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>17757555</v>
       </c>
       <c r="B20" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>15310686</v>
       </c>
       <c r="B21" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>18462585</v>
       </c>
       <c r="B22" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>18638143</v>
       </c>
       <c r="B23" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>18358434</v>
       </c>
       <c r="B24" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>18363086</v>
       </c>
       <c r="B25" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>18706466</v>
       </c>
       <c r="B26" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>17976464</v>
       </c>
       <c r="B27" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>15310340</v>
       </c>
       <c r="B28" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>16183555</v>
       </c>
       <c r="B29" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>18446996</v>
       </c>
       <c r="B30" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>18463325</v>
       </c>
       <c r="B31" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>18610900</v>
       </c>
       <c r="B32" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>16175433</v>
       </c>
       <c r="B33" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>8594304</v>
       </c>
       <c r="B34" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>18639900</v>
       </c>
       <c r="B35" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>18606938</v>
       </c>
       <c r="B36" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>17968066</v>
       </c>
       <c r="B37" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>18462979</v>
       </c>
       <c r="B38" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>18592846</v>
       </c>
       <c r="B39" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>16057502</v>
       </c>
       <c r="B40" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>15471003</v>
       </c>
       <c r="B41" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>17494382</v>
       </c>
       <c r="B42" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>15833648</v>
       </c>
       <c r="B43" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>9325232</v>
       </c>
       <c r="B44" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>18380685</v>
       </c>
       <c r="B45" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>13684645</v>
       </c>
       <c r="B46" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>15743886</v>
       </c>
       <c r="B47" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>18055304</v>
       </c>
       <c r="B48" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>6337847</v>
       </c>
       <c r="B49" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>6072242</v>
       </c>
       <c r="B50" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>18494510</v>
       </c>
       <c r="B51" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>6343490</v>
       </c>
       <c r="B52" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>18607039</v>
       </c>
       <c r="B53" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>18709835</v>
       </c>
       <c r="B54" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>6347967</v>
       </c>
       <c r="B55" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>15914456</v>
       </c>
       <c r="B56" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>18638146</v>
       </c>
       <c r="B57" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>18607040</v>
       </c>
       <c r="B58" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>16002078</v>
       </c>
       <c r="B59" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>836361291</v>
       </c>
       <c r="B60" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>18651916</v>
       </c>
       <c r="B61" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>15379533</v>
       </c>
       <c r="B62" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>15273284</v>
       </c>
       <c r="B63" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>15286014</v>
       </c>
       <c r="B64" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>16591614</v>
       </c>
       <c r="B65" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>18278193</v>
       </c>
       <c r="B66" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>18438115</v>
       </c>
       <c r="B67" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>6344268</v>
       </c>
       <c r="B68" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>19031223</v>
       </c>
       <c r="B69" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>913469626</v>
       </c>
       <c r="B70" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>16650432</v>
       </c>
       <c r="B71" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>16112906</v>
       </c>
       <c r="B72" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>15508932</v>
       </c>
       <c r="B73" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>15471051</v>
       </c>
       <c r="B74" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>17771453</v>
       </c>
       <c r="B75" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>18709833</v>
       </c>
       <c r="B76" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>15315078</v>
       </c>
       <c r="B77" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>14652432</v>
       </c>
       <c r="B78" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>6072248</v>
       </c>
       <c r="B79" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>6344408</v>
       </c>
       <c r="B80" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>12228487</v>
       </c>
       <c r="B81" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>6072235</v>
       </c>
       <c r="B82" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>6336327</v>
       </c>
       <c r="B83" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>10299228</v>
       </c>
       <c r="B84" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>16650115</v>
       </c>
       <c r="B85" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>912467251</v>
       </c>
       <c r="B86" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>15733894</v>
       </c>
       <c r="B87" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>1115070798</v>
       </c>
       <c r="B88" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>16175292</v>
       </c>
       <c r="B89" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>1114242008</v>
       </c>
       <c r="B90" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>16239943</v>
       </c>
       <c r="B91" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>15808166</v>
       </c>
       <c r="B92" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>17546623</v>
       </c>
       <c r="B93" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>923996664</v>
       </c>
       <c r="B94" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>925140513</v>
       </c>
       <c r="B95" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>16999221</v>
       </c>
       <c r="B96" t="n">
-        <v>205499.5</v>
+        <v>71677.55</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>17706766</v>
       </c>
       <c r="B97" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>884130905</v>
       </c>
       <c r="B98" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>17892639</v>
       </c>
       <c r="B99" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>1115064487</v>
       </c>
       <c r="B100" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>16069914</v>
       </c>
       <c r="B101" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>17804418</v>
       </c>
       <c r="B102" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>15399347</v>
       </c>
       <c r="B103" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>6338644</v>
       </c>
       <c r="B104" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>18373357</v>
       </c>
       <c r="B105" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>6072334</v>
       </c>
       <c r="B106" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>6344425</v>
       </c>
       <c r="B107" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>16269736</v>
       </c>
       <c r="B108" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>852319875</v>
       </c>
       <c r="B109" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>18607311</v>
       </c>
       <c r="B110" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>17706729</v>
       </c>
       <c r="B111" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>1113103758</v>
       </c>
       <c r="B112" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>18723703</v>
       </c>
       <c r="B113" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>6193660</v>
       </c>
       <c r="B114" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>6072240</v>
       </c>
       <c r="B115" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>16221362</v>
       </c>
       <c r="B116" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>1121491600</v>
       </c>
       <c r="B117" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>16650434</v>
       </c>
       <c r="B118" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>6832552</v>
       </c>
       <c r="B119" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>18426503</v>
       </c>
       <c r="B120" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>876021146</v>
       </c>
       <c r="B121" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>18247665</v>
       </c>
       <c r="B122" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>18592847</v>
       </c>
       <c r="B123" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>19031156</v>
       </c>
       <c r="B124" t="n">
-        <v>17999</v>
+        <v>12564.26</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>15743889</v>
       </c>
       <c r="B125" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>6344280</v>
       </c>
       <c r="B126" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>16239941</v>
       </c>
       <c r="B127" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>16927378</v>
       </c>
       <c r="B128" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>19031161</v>
       </c>
       <c r="B129" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>1116722138</v>
       </c>
       <c r="B130" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>9011551</v>
       </c>
       <c r="B131" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>18606723</v>
       </c>
       <c r="B132" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>1108269405</v>
       </c>
       <c r="B133" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>18337812</v>
       </c>
       <c r="B134" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>15310695</v>
       </c>
       <c r="B135" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>914875838</v>
       </c>
       <c r="B136" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>912468225</v>
       </c>
       <c r="B137" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>16052514</v>
       </c>
       <c r="B138" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>18589165</v>
       </c>
       <c r="B139" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>1114330209</v>
       </c>
       <c r="B140" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>17805819</v>
       </c>
       <c r="B141" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>881691036</v>
       </c>
       <c r="B142" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>18919702</v>
       </c>
       <c r="B143" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>16111563</v>
       </c>
       <c r="B144" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>15286958</v>
       </c>
       <c r="B145" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>6072294</v>
       </c>
       <c r="B146" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>10208562</v>
       </c>
       <c r="B147" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>18593256</v>
       </c>
       <c r="B148" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>6832553</v>
       </c>
       <c r="B149" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>896586074</v>
       </c>
       <c r="B150" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>15273294</v>
       </c>
       <c r="B151" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>1111603848</v>
       </c>
       <c r="B152" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>15315837</v>
       </c>
       <c r="B153" t="n">
-        <v>205499.5</v>
+        <v>56899.24</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>931087249</v>
       </c>
       <c r="B154" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>1117946176</v>
       </c>
       <c r="B155" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>15293527</v>
       </c>
       <c r="B156" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>16121293</v>
       </c>
       <c r="B157" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>885041279</v>
       </c>
       <c r="B158" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>15549161</v>
       </c>
       <c r="B159" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>831673946</v>
       </c>
       <c r="B160" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>8922565</v>
       </c>
       <c r="B161" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>6832550</v>
       </c>
       <c r="B162" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>9697690</v>
       </c>
       <c r="B163" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>9406415</v>
       </c>
       <c r="B164" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>19037261</v>
       </c>
       <c r="B165" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>637538441</v>
       </c>
       <c r="B166" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>907956288</v>
       </c>
       <c r="B167" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>913240593</v>
       </c>
       <c r="B168" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>797888276</v>
       </c>
       <c r="B169" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>14438843</v>
       </c>
       <c r="B170" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>931426178</v>
       </c>
       <c r="B171" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>11978943</v>
       </c>
       <c r="B172" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>15308482</v>
       </c>
       <c r="B173" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>886142281</v>
       </c>
       <c r="B174" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>15507051</v>
       </c>
       <c r="B175" t="n">
-        <v>205499.5</v>
+        <v>66751.45</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>1119665436</v>
       </c>
       <c r="B176" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>727049560</v>
       </c>
       <c r="B177" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>911184116</v>
       </c>
       <c r="B178" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>16060542</v>
       </c>
       <c r="B179" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1120906780</v>
       </c>
       <c r="B180" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>875882215</v>
       </c>
       <c r="B181" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>1103851186</v>
       </c>
       <c r="B182" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>18606284</v>
       </c>
       <c r="B183" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>907707957</v>
       </c>
       <c r="B184" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>14593572</v>
       </c>
       <c r="B185" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>1120187366</v>
       </c>
       <c r="B186" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>882442458</v>
       </c>
       <c r="B187" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>17187386</v>
       </c>
       <c r="B188" t="n">
-        <v>205499.5</v>
+        <v>106160.3</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>17940268</v>
       </c>
       <c r="B189" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>18519572</v>
       </c>
       <c r="B190" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>909598017</v>
       </c>
       <c r="B191" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>754710815</v>
       </c>
       <c r="B192" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>16195298</v>
       </c>
       <c r="B193" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>15382761</v>
       </c>
       <c r="B194" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>18593354</v>
       </c>
       <c r="B195" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>18607275</v>
       </c>
       <c r="B196" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>1108282487</v>
       </c>
       <c r="B197" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>6337154</v>
       </c>
       <c r="B198" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>15978838</v>
       </c>
       <c r="B199" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>919145833</v>
       </c>
       <c r="B200" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>933641708</v>
       </c>
       <c r="B201" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>1115052581</v>
       </c>
       <c r="B202" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>11426790</v>
       </c>
       <c r="B203" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>904051162</v>
       </c>
       <c r="B204" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>881650004</v>
       </c>
       <c r="B205" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>15379152</v>
       </c>
       <c r="B206" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>934873402</v>
       </c>
       <c r="B207" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>904188626</v>
       </c>
       <c r="B208" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>16030226</v>
       </c>
       <c r="B209" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>11321063</v>
       </c>
       <c r="B210" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>930202021</v>
       </c>
       <c r="B211" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>1121772402</v>
       </c>
       <c r="B212" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>918305956</v>
       </c>
       <c r="B213" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>15288715</v>
       </c>
       <c r="B214" t="n">
-        <v>205499.5</v>
+        <v>66751.45</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>1101868371</v>
       </c>
       <c r="B215" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>916064750</v>
       </c>
       <c r="B216" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>1120044115</v>
       </c>
       <c r="B217" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>1120933966</v>
       </c>
       <c r="B218" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1122513378</v>
       </c>
       <c r="B219" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>935827684</v>
       </c>
       <c r="B220" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>11754916</v>
       </c>
       <c r="B221" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>10075001</v>
       </c>
       <c r="B222" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>15378953</v>
       </c>
       <c r="B223" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>880202197</v>
       </c>
       <c r="B224" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>1110791510</v>
       </c>
       <c r="B225" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>6354570</v>
       </c>
       <c r="B226" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>881226624</v>
       </c>
       <c r="B227" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>923577172</v>
       </c>
       <c r="B228" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>1115644461</v>
       </c>
       <c r="B229" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>872788286</v>
       </c>
       <c r="B230" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>1123246945</v>
       </c>
       <c r="B231" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>11888242</v>
       </c>
       <c r="B232" t="n">
-        <v>205499.5</v>
+        <v>56899.24</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>1114923275</v>
       </c>
       <c r="B233" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>886622659</v>
       </c>
       <c r="B234" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>919153189</v>
       </c>
       <c r="B235" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>811171609</v>
       </c>
       <c r="B236" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>1114401671</v>
       </c>
       <c r="B237" t="n">
-        <v>25535.5</v>
+        <v>32268.7</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>913241236</v>
       </c>
       <c r="B238" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>7562787</v>
       </c>
       <c r="B239" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>1121766180</v>
       </c>
       <c r="B240" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>15349548</v>
       </c>
       <c r="B241" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>859227471</v>
       </c>
       <c r="B242" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>901178191</v>
       </c>
       <c r="B243" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>15531624</v>
       </c>
       <c r="B244" t="n">
-        <v>40281</v>
+        <v>51973.12</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>1121186626</v>
       </c>
       <c r="B245" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>6416458</v>
       </c>
       <c r="B246" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>809321857</v>
       </c>
       <c r="B247" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>877476405</v>
       </c>
       <c r="B248" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>936076884</v>
       </c>
       <c r="B249" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>855463000</v>
       </c>
       <c r="B250" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>1111659291</v>
       </c>
       <c r="B251" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>663572631</v>
       </c>
       <c r="B252" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>15808169</v>
       </c>
       <c r="B253" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>15288978</v>
       </c>
       <c r="B254" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>914377691</v>
       </c>
       <c r="B255" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>15470092</v>
       </c>
       <c r="B256" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>19077796</v>
       </c>
       <c r="B257" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>15543391</v>
       </c>
       <c r="B258" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>15699159</v>
       </c>
       <c r="B259" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>6347917</v>
       </c>
       <c r="B260" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>15315844</v>
       </c>
       <c r="B261" t="n">
-        <v>205499.5</v>
+        <v>101234.2</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>1116583780</v>
       </c>
       <c r="B262" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>923486327</v>
       </c>
       <c r="B263" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>797024404</v>
       </c>
       <c r="B264" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>11930357</v>
       </c>
       <c r="B265" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>917608253</v>
       </c>
       <c r="B266" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>700512792</v>
       </c>
       <c r="B267" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>1102037091</v>
       </c>
       <c r="B268" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>1122989198</v>
       </c>
       <c r="B269" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>756783069</v>
       </c>
       <c r="B270" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>9019135</v>
       </c>
       <c r="B271" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>925274582</v>
       </c>
       <c r="B272" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>915056367</v>
       </c>
       <c r="B273" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>15291008</v>
       </c>
       <c r="B274" t="n">
-        <v>40281</v>
+        <v>32268.7</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>874130897</v>
       </c>
       <c r="B275" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>1129715800</v>
       </c>
       <c r="B276" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>822514455</v>
       </c>
       <c r="B277" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>868732286</v>
       </c>
       <c r="B278" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>879033872</v>
       </c>
       <c r="B279" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>750311717</v>
       </c>
       <c r="B280" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>791953982</v>
       </c>
       <c r="B281" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>931500898</v>
       </c>
       <c r="B282" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>6352417</v>
       </c>
       <c r="B283" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>923002708</v>
       </c>
       <c r="B284" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>1116419841</v>
       </c>
       <c r="B285" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>11754895</v>
       </c>
       <c r="B286" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>902592484</v>
       </c>
       <c r="B287" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>6072318</v>
       </c>
       <c r="B288" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>741588326</v>
       </c>
       <c r="B289" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>1119145884</v>
       </c>
       <c r="B290" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>15512192</v>
       </c>
       <c r="B291" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>934239363</v>
       </c>
       <c r="B292" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>878024478</v>
       </c>
       <c r="B293" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>918336819</v>
       </c>
       <c r="B294" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>915054189</v>
       </c>
       <c r="B295" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>1131913043</v>
       </c>
       <c r="B296" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>900499833</v>
       </c>
       <c r="B297" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>1110220987</v>
       </c>
       <c r="B298" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>897839490</v>
       </c>
       <c r="B299" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>15555358</v>
       </c>
       <c r="B300" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>933449597</v>
       </c>
       <c r="B301" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>924690025</v>
       </c>
       <c r="B302" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>18373479</v>
       </c>
       <c r="B303" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>914371954</v>
       </c>
       <c r="B304" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>1114137205</v>
       </c>
       <c r="B305" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>860221504</v>
       </c>
       <c r="B306" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>874140292</v>
       </c>
       <c r="B307" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>9330542</v>
       </c>
       <c r="B308" t="n">
-        <v>205499.5</v>
+        <v>66751.45</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>1119098543</v>
       </c>
       <c r="B309" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>815795530</v>
       </c>
       <c r="B310" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>853212986</v>
       </c>
       <c r="B311" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>15289416</v>
       </c>
       <c r="B312" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>1114272384</v>
       </c>
       <c r="B313" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>844701565</v>
       </c>
       <c r="B314" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>15306522</v>
       </c>
       <c r="B315" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>1116948166</v>
       </c>
       <c r="B316" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>15577045</v>
       </c>
       <c r="B317" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>907304117</v>
       </c>
       <c r="B318" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>906761782</v>
       </c>
       <c r="B319" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>884338797</v>
       </c>
       <c r="B320" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>918610219</v>
       </c>
       <c r="B321" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>1107510516</v>
       </c>
       <c r="B322" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>16002080</v>
       </c>
       <c r="B323" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>844700874</v>
       </c>
       <c r="B324" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>1112955334</v>
       </c>
       <c r="B325" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>881662962</v>
       </c>
       <c r="B326" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>15277655</v>
       </c>
       <c r="B327" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>830812443</v>
       </c>
       <c r="B328" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>691348825</v>
       </c>
       <c r="B329" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>1111465624</v>
       </c>
       <c r="B330" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>814778137</v>
       </c>
       <c r="B331" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>776353377</v>
       </c>
       <c r="B332" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>863255350</v>
       </c>
       <c r="B333" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>15834838</v>
       </c>
       <c r="B334" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>842796285</v>
       </c>
       <c r="B335" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>15542339</v>
       </c>
       <c r="B336" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>1116668330</v>
       </c>
       <c r="B337" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>1105899348</v>
       </c>
       <c r="B338" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>1108943251</v>
       </c>
       <c r="B339" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>18607184</v>
       </c>
       <c r="B340" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>15377986</v>
       </c>
       <c r="B341" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>913471690</v>
       </c>
       <c r="B342" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>871240547</v>
       </c>
       <c r="B343" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>1128201177</v>
       </c>
       <c r="B344" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>1110928918</v>
       </c>
       <c r="B345" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>1117377342</v>
       </c>
       <c r="B346" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>929081447</v>
       </c>
       <c r="B347" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>929569629</v>
       </c>
       <c r="B348" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>15306511</v>
       </c>
       <c r="B349" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>871505338</v>
       </c>
       <c r="B350" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>17805815</v>
       </c>
       <c r="B351" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>6417063</v>
       </c>
       <c r="B352" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>1116593785</v>
       </c>
       <c r="B353" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>897036516</v>
       </c>
       <c r="B354" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>6350347</v>
       </c>
       <c r="B355" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>880742482</v>
       </c>
       <c r="B356" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>1109062533</v>
       </c>
       <c r="B357" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>806958924</v>
       </c>
       <c r="B358" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>1112490227</v>
       </c>
       <c r="B359" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>6344245</v>
       </c>
       <c r="B360" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>18373096</v>
       </c>
       <c r="B361" t="n">
-        <v>40281</v>
+        <v>32268.7</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>879456567</v>
       </c>
       <c r="B362" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>860503850</v>
       </c>
       <c r="B363" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>929821070</v>
       </c>
       <c r="B364" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>15345429</v>
       </c>
       <c r="B365" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>626647115</v>
       </c>
       <c r="B366" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>15834851</v>
       </c>
       <c r="B367" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>7562783</v>
       </c>
       <c r="B368" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>18592196</v>
       </c>
       <c r="B369" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>928046534</v>
       </c>
       <c r="B370" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>15393128</v>
       </c>
       <c r="B371" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>1102261779</v>
       </c>
       <c r="B372" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>928283324</v>
       </c>
       <c r="B373" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>811585039</v>
       </c>
       <c r="B374" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>627563068</v>
       </c>
       <c r="B375" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>15397849</v>
       </c>
       <c r="B376" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>1131648902</v>
       </c>
       <c r="B377" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>689256562</v>
       </c>
       <c r="B378" t="n">
-        <v>25535.5</v>
+        <v>32268.7</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>15377809</v>
       </c>
       <c r="B379" t="n">
-        <v>40281</v>
+        <v>32268.7</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>923479834</v>
       </c>
       <c r="B380" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>922780812</v>
       </c>
       <c r="B381" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>751765880</v>
       </c>
       <c r="B382" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>904850061</v>
       </c>
       <c r="B383" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>846446324</v>
       </c>
       <c r="B384" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>758648886</v>
       </c>
       <c r="B385" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>1118947238</v>
       </c>
       <c r="B386" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>909691137</v>
       </c>
       <c r="B387" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>899695260</v>
       </c>
       <c r="B388" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>18536588</v>
       </c>
       <c r="B389" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>1128931006</v>
       </c>
       <c r="B390" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>15257556</v>
       </c>
       <c r="B391" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>880262388</v>
       </c>
       <c r="B392" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>855319185</v>
       </c>
       <c r="B393" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>1105938796</v>
       </c>
       <c r="B394" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>898087370</v>
       </c>
       <c r="B395" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>918504791</v>
       </c>
       <c r="B396" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>825545561</v>
       </c>
       <c r="B397" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>15510741</v>
       </c>
       <c r="B398" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>6347793</v>
       </c>
       <c r="B399" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>906380357</v>
       </c>
       <c r="B400" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>16160737</v>
       </c>
       <c r="B401" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>1108798382</v>
       </c>
       <c r="B402" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>923018277</v>
       </c>
       <c r="B403" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>1108718132</v>
       </c>
       <c r="B404" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>1102097015</v>
       </c>
       <c r="B405" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>930504722</v>
       </c>
       <c r="B406" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>789915235</v>
       </c>
       <c r="B407" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>919625614</v>
       </c>
       <c r="B408" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>1126513331</v>
       </c>
       <c r="B409" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>913647114</v>
       </c>
       <c r="B410" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>1122136034</v>
       </c>
       <c r="B411" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>1128077143</v>
       </c>
       <c r="B412" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>1123612509</v>
       </c>
       <c r="B413" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>18607312</v>
       </c>
       <c r="B414" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>920341235</v>
       </c>
       <c r="B415" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>897028778</v>
       </c>
       <c r="B416" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>757515580</v>
       </c>
       <c r="B417" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>1113773823</v>
       </c>
       <c r="B418" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>907007451</v>
       </c>
       <c r="B419" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>1128915848</v>
       </c>
       <c r="B420" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>1106924517</v>
       </c>
       <c r="B421" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>934679851</v>
       </c>
       <c r="B422" t="n">
-        <v>205499.5</v>
+        <v>61825.34</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>855542033</v>
       </c>
       <c r="B423" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>790636789</v>
       </c>
       <c r="B424" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>886067876</v>
       </c>
       <c r="B425" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>856346104</v>
       </c>
       <c r="B426" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>924692131</v>
       </c>
       <c r="B427" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>15289893</v>
       </c>
       <c r="B428" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>926241951</v>
       </c>
       <c r="B429" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>1102253328</v>
       </c>
       <c r="B430" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>881615881</v>
       </c>
       <c r="B431" t="n">
-        <v>205499.5</v>
+        <v>135716.94</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>1123756783</v>
       </c>
       <c r="B432" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>864010590</v>
       </c>
       <c r="B433" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>880200813</v>
       </c>
       <c r="B434" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>904717308</v>
       </c>
       <c r="B435" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>835907400</v>
       </c>
       <c r="B436" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>647289957</v>
       </c>
       <c r="B437" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>897380462</v>
       </c>
       <c r="B438" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>1110345992</v>
       </c>
       <c r="B439" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>636865832</v>
       </c>
       <c r="B440" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>896881469</v>
       </c>
       <c r="B441" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>859749359</v>
       </c>
       <c r="B442" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>922635377</v>
       </c>
       <c r="B443" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>852331351</v>
       </c>
       <c r="B444" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>863634910</v>
       </c>
       <c r="B445" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>1121571067</v>
       </c>
       <c r="B446" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>915601227</v>
       </c>
       <c r="B447" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>9697688</v>
       </c>
       <c r="B448" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>1116827748</v>
       </c>
       <c r="B449" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>933220266</v>
       </c>
       <c r="B450" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>829924739</v>
       </c>
       <c r="B451" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>818597500</v>
       </c>
       <c r="B452" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>1107315322</v>
       </c>
       <c r="B453" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>909205435</v>
       </c>
       <c r="B454" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>928410242</v>
       </c>
       <c r="B455" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>868707446</v>
       </c>
       <c r="B456" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>1133414220</v>
       </c>
       <c r="B457" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>929613041</v>
       </c>
       <c r="B458" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>731579326</v>
       </c>
       <c r="B459" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>935630827</v>
       </c>
       <c r="B460" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>15560811</v>
       </c>
       <c r="B461" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>877185663</v>
       </c>
       <c r="B462" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>925139246</v>
       </c>
       <c r="B463" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>852525148</v>
       </c>
       <c r="B464" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>1100813041</v>
       </c>
       <c r="B465" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>1108214045</v>
       </c>
       <c r="B466" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>750314214</v>
       </c>
       <c r="B467" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>751767608</v>
       </c>
       <c r="B468" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>735466495</v>
       </c>
       <c r="B469" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>904294521</v>
       </c>
       <c r="B470" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>1102633213</v>
       </c>
       <c r="B471" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>1122844734</v>
       </c>
       <c r="B472" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>1129827842</v>
       </c>
       <c r="B473" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>802083630</v>
       </c>
       <c r="B474" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>880139394</v>
       </c>
       <c r="B475" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>833053436</v>
       </c>
       <c r="B476" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>1109382783</v>
       </c>
       <c r="B477" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>918398164</v>
       </c>
       <c r="B478" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>877523252</v>
       </c>
       <c r="B479" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>903574202</v>
       </c>
       <c r="B480" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>1110063500</v>
       </c>
       <c r="B481" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>1108039014</v>
       </c>
       <c r="B482" t="n">
-        <v>205499.5</v>
+        <v>106160.3</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>860833475</v>
       </c>
       <c r="B483" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>15972300</v>
       </c>
       <c r="B484" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>1106487821</v>
       </c>
       <c r="B485" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>855393952</v>
       </c>
       <c r="B486" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>695474280</v>
       </c>
       <c r="B487" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>693323156</v>
       </c>
       <c r="B488" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>907584492</v>
       </c>
       <c r="B489" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>847711432</v>
       </c>
       <c r="B490" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>807261579</v>
       </c>
       <c r="B491" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>791951128</v>
       </c>
       <c r="B492" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>770051241</v>
       </c>
       <c r="B493" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>15391124</v>
       </c>
       <c r="B494" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>620984017</v>
       </c>
       <c r="B495" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>916202362</v>
       </c>
       <c r="B496" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>905466495</v>
       </c>
       <c r="B497" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>846611029</v>
       </c>
       <c r="B498" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>1128229626</v>
       </c>
       <c r="B499" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>903409780</v>
       </c>
       <c r="B500" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>818578958</v>
       </c>
       <c r="B501" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>882240424</v>
       </c>
       <c r="B502" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>752221762</v>
       </c>
       <c r="B503" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>875968196</v>
       </c>
       <c r="B504" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>17921575</v>
       </c>
       <c r="B505" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>881775258</v>
       </c>
       <c r="B506" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>792142140</v>
       </c>
       <c r="B507" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>15345433</v>
       </c>
       <c r="B508" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>15277656</v>
       </c>
       <c r="B509" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>934885586</v>
       </c>
       <c r="B510" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>15377856</v>
       </c>
       <c r="B511" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>918190794</v>
       </c>
       <c r="B512" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>866942933</v>
       </c>
       <c r="B513" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>904805878</v>
       </c>
       <c r="B514" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>923292241</v>
       </c>
       <c r="B515" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>8594307</v>
       </c>
       <c r="B516" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>867418064</v>
       </c>
       <c r="B517" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>866144610</v>
       </c>
       <c r="B518" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>847111755</v>
       </c>
       <c r="B519" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr"/>
@@ -26008,7 +26008,7 @@
         <v>900053427</v>
       </c>
       <c r="B520" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>898608273</v>
       </c>
       <c r="B521" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>1133781777</v>
       </c>
       <c r="B522" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>756988396</v>
       </c>
       <c r="B523" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>922036332</v>
       </c>
       <c r="B524" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>905810771</v>
       </c>
       <c r="B525" t="n">
-        <v>40281</v>
+        <v>32268.7</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>791497815</v>
       </c>
       <c r="B526" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>929617536</v>
       </c>
       <c r="B527" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>13997278</v>
       </c>
       <c r="B528" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>1116494415</v>
       </c>
       <c r="B529" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>925305443</v>
       </c>
       <c r="B530" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>933637052</v>
       </c>
       <c r="B531" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>925862128</v>
       </c>
       <c r="B532" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>927700257</v>
       </c>
       <c r="B533" t="n">
-        <v>205499.5</v>
+        <v>101234.2</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>1123204733</v>
       </c>
       <c r="B534" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>899725627</v>
       </c>
       <c r="B535" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>861011524</v>
       </c>
       <c r="B536" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>1106205173</v>
       </c>
       <c r="B537" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>863044078</v>
       </c>
       <c r="B538" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>1128389350</v>
       </c>
       <c r="B539" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>881935414</v>
       </c>
       <c r="B540" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>17810776</v>
       </c>
       <c r="B541" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>918336653</v>
       </c>
       <c r="B542" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>901406795</v>
       </c>
       <c r="B543" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>1120116605</v>
       </c>
       <c r="B544" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>1123223921</v>
       </c>
       <c r="B545" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>1119456120</v>
       </c>
       <c r="B546" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>916610782</v>
       </c>
       <c r="B547" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>1121720126</v>
       </c>
       <c r="B548" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>866112134</v>
       </c>
       <c r="B549" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>908820934</v>
       </c>
       <c r="B550" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>15274195</v>
       </c>
       <c r="B551" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>880121815</v>
       </c>
       <c r="B552" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>1125616673</v>
       </c>
       <c r="B553" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>872790129</v>
       </c>
       <c r="B554" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>1110932719</v>
       </c>
       <c r="B555" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>852132090</v>
       </c>
       <c r="B556" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>885151311</v>
       </c>
       <c r="B557" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>904960817</v>
       </c>
       <c r="B558" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>881657526</v>
       </c>
       <c r="B559" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>1102620003</v>
       </c>
       <c r="B560" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>1107230502</v>
       </c>
       <c r="B561" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>919623165</v>
       </c>
       <c r="B562" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>637094999</v>
       </c>
       <c r="B563" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>1130769315</v>
       </c>
       <c r="B564" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>16638460</v>
       </c>
       <c r="B565" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>1116303909</v>
       </c>
       <c r="B566" t="n">
-        <v>205499.5</v>
+        <v>51973.12</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>660259283</v>
       </c>
       <c r="B567" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>929309774</v>
       </c>
       <c r="B568" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>886025776</v>
       </c>
       <c r="B569" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>928622677</v>
       </c>
       <c r="B570" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>1117944671</v>
       </c>
       <c r="B571" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>1100655107</v>
       </c>
       <c r="B572" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>781303325</v>
       </c>
       <c r="B573" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>850055811</v>
       </c>
       <c r="B574" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>1122459537</v>
       </c>
       <c r="B575" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>11333329</v>
       </c>
       <c r="B576" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C576" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>1122819322</v>
       </c>
       <c r="B577" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>1127558458</v>
       </c>
       <c r="B578" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>816705228</v>
       </c>
       <c r="B579" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>918903304</v>
       </c>
       <c r="B580" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>904973666</v>
       </c>
       <c r="B581" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>901195475</v>
       </c>
       <c r="B582" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>1109453208</v>
       </c>
       <c r="B583" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>870991837</v>
       </c>
       <c r="B584" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>909354425</v>
       </c>
       <c r="B585" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>882831864</v>
       </c>
       <c r="B586" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>874298085</v>
       </c>
       <c r="B587" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>811744902</v>
       </c>
       <c r="B588" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>1112600200</v>
       </c>
       <c r="B589" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>905832935</v>
       </c>
       <c r="B590" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>13997250</v>
       </c>
       <c r="B591" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>1100839117</v>
       </c>
       <c r="B592" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>933904530</v>
       </c>
       <c r="B593" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>903425903</v>
       </c>
       <c r="B594" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>1129769741</v>
       </c>
       <c r="B595" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>842364117</v>
       </c>
       <c r="B596" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>869779181</v>
       </c>
       <c r="B597" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>886777373</v>
       </c>
       <c r="B598" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>652450311</v>
       </c>
       <c r="B599" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>1127943758</v>
       </c>
       <c r="B600" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>880069293</v>
       </c>
       <c r="B601" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>817310936</v>
       </c>
       <c r="B602" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>847740341</v>
       </c>
       <c r="B603" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>916046369</v>
       </c>
       <c r="B604" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>923018614</v>
       </c>
       <c r="B605" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>923918528</v>
       </c>
       <c r="B606" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>903102356</v>
       </c>
       <c r="B607" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C607" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>1111210435</v>
       </c>
       <c r="B608" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>1122501270</v>
       </c>
       <c r="B609" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>886244956</v>
       </c>
       <c r="B610" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C610" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>851984822</v>
       </c>
       <c r="B611" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C611" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>928098822</v>
       </c>
       <c r="B612" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C612" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>904520230</v>
       </c>
       <c r="B613" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>901844440</v>
       </c>
       <c r="B614" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>18732182</v>
       </c>
       <c r="B615" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C615" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>16008108</v>
       </c>
       <c r="B616" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>1111534935</v>
       </c>
       <c r="B617" t="n">
-        <v>25535.5</v>
+        <v>32268.7</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>886459798</v>
       </c>
       <c r="B618" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>836361277</v>
       </c>
       <c r="B619" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>880120642</v>
       </c>
       <c r="B620" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C620" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>903615057</v>
       </c>
       <c r="B621" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C621" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>934526968</v>
       </c>
       <c r="B622" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C622" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>816707854</v>
       </c>
       <c r="B623" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>1103241890</v>
       </c>
       <c r="B624" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>1116993867</v>
       </c>
       <c r="B625" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>880204149</v>
       </c>
       <c r="B626" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>912767935</v>
       </c>
       <c r="B627" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>924881030</v>
       </c>
       <c r="B628" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>884705024</v>
       </c>
       <c r="B629" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>899848793</v>
       </c>
       <c r="B630" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C630" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>933921794</v>
       </c>
       <c r="B631" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C631" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>1110235145</v>
       </c>
       <c r="B632" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>932731958</v>
       </c>
       <c r="B633" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C633" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>870837013</v>
       </c>
       <c r="B634" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C634" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>1103322437</v>
       </c>
       <c r="B635" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>1106209939</v>
       </c>
       <c r="B636" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C636" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>9697673</v>
       </c>
       <c r="B637" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>871887989</v>
       </c>
       <c r="B638" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C638" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>883859558</v>
       </c>
       <c r="B639" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>856346919</v>
       </c>
       <c r="B640" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>880566469</v>
       </c>
       <c r="B641" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C641" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>1116634690</v>
       </c>
       <c r="B642" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C642" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>909668042</v>
       </c>
       <c r="B643" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C643" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>825021690</v>
       </c>
       <c r="B644" t="n">
-        <v>40281</v>
+        <v>42120.91</v>
       </c>
       <c r="C644" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>910533989</v>
       </c>
       <c r="B645" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C645" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>695473965</v>
       </c>
       <c r="B646" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C646" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>881678513</v>
       </c>
       <c r="B647" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C647" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>15317359</v>
       </c>
       <c r="B648" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C648" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>933506487</v>
       </c>
       <c r="B649" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C649" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>857324227</v>
       </c>
       <c r="B650" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>11754899</v>
       </c>
       <c r="B651" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>813439006</v>
       </c>
       <c r="B652" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>904376476</v>
       </c>
       <c r="B653" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>852132907</v>
       </c>
       <c r="B654" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>781985273</v>
       </c>
       <c r="B655" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>6355361</v>
       </c>
       <c r="B656" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>897831873</v>
       </c>
       <c r="B657" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>1130201053</v>
       </c>
       <c r="B658" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>792335904</v>
       </c>
       <c r="B659" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>829673651</v>
       </c>
       <c r="B660" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>1116467121</v>
       </c>
       <c r="B661" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>815764809</v>
       </c>
       <c r="B662" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>838121066</v>
       </c>
       <c r="B663" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>910322199</v>
       </c>
       <c r="B664" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>916572980</v>
       </c>
       <c r="B665" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C665" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>1113777095</v>
       </c>
       <c r="B666" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C666" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>834748359</v>
       </c>
       <c r="B667" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C667" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>916179844</v>
       </c>
       <c r="B668" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C668" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>1116379718</v>
       </c>
       <c r="B669" t="n">
-        <v>9812.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C669" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>1122534031</v>
       </c>
       <c r="B670" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>6366638</v>
       </c>
       <c r="B671" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>913980614</v>
       </c>
       <c r="B672" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>907347090</v>
       </c>
       <c r="B673" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>15914241</v>
       </c>
       <c r="B674" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C674" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>1112421727</v>
       </c>
       <c r="B675" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>735924725</v>
       </c>
       <c r="B676" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>859225448</v>
       </c>
       <c r="B677" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>1121713922</v>
       </c>
       <c r="B678" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>636866271</v>
       </c>
       <c r="B679" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C679" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>879390802</v>
       </c>
       <c r="B680" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>910538550</v>
       </c>
       <c r="B681" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>880726037</v>
       </c>
       <c r="B682" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>1108113886</v>
       </c>
       <c r="B683" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>1116104059</v>
       </c>
       <c r="B684" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>1133517467</v>
       </c>
       <c r="B685" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C685" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>867600961</v>
       </c>
       <c r="B686" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>886629945</v>
       </c>
       <c r="B687" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>932926235</v>
       </c>
       <c r="B688" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>1109708637</v>
       </c>
       <c r="B689" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>847290572</v>
       </c>
       <c r="B690" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C690" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>1102996681</v>
       </c>
       <c r="B691" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C691" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>16625999</v>
       </c>
       <c r="B692" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C692" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>1109019202</v>
       </c>
       <c r="B693" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C693" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>916729368</v>
       </c>
       <c r="B694" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C694" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>1103161622</v>
       </c>
       <c r="B695" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C695" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>15397502</v>
       </c>
       <c r="B696" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C696" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>828351392</v>
       </c>
       <c r="B697" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C697" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>880141329</v>
       </c>
       <c r="B698" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C698" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>14663094</v>
       </c>
       <c r="B699" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C699" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>1119124101</v>
       </c>
       <c r="B700" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C700" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>881101698</v>
       </c>
       <c r="B701" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C701" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>15313321</v>
       </c>
       <c r="B702" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C702" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>923007213</v>
       </c>
       <c r="B703" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C703" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>883861263</v>
       </c>
       <c r="B704" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C704" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>863634914</v>
       </c>
       <c r="B705" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C705" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>858823461</v>
       </c>
       <c r="B706" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C706" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>10208582</v>
       </c>
       <c r="B707" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C707" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>785557522</v>
       </c>
       <c r="B708" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C708" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>727692298</v>
       </c>
       <c r="B709" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C709" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>871168040</v>
       </c>
       <c r="B710" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C710" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>1129267596</v>
       </c>
       <c r="B711" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C711" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>866115853</v>
       </c>
       <c r="B712" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C712" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>1120208313</v>
       </c>
       <c r="B713" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C713" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>837495488</v>
       </c>
       <c r="B714" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C714" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>1111757301</v>
       </c>
       <c r="B715" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C715" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>1120250902</v>
       </c>
       <c r="B716" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C716" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>727027553</v>
       </c>
       <c r="B717" t="n">
-        <v>205499.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C717" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>14097798</v>
       </c>
       <c r="B718" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C718" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>899539794</v>
       </c>
       <c r="B719" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C719" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>884674524</v>
       </c>
       <c r="B720" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C720" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>911170713</v>
       </c>
       <c r="B721" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C721" t="inlineStr">
         <is>
@@ -35316,7 +35316,7 @@
         <v>1136322034</v>
       </c>
       <c r="B722" t="n">
-        <v>6423</v>
+        <v>7638.16</v>
       </c>
       <c r="C722" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>872770953</v>
       </c>
       <c r="B723" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C723" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>862642327</v>
       </c>
       <c r="B724" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C724" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>15257546</v>
       </c>
       <c r="B725" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C725" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>1119582526</v>
       </c>
       <c r="B726" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C726" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>852132093</v>
       </c>
       <c r="B727" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>935511507</v>
       </c>
       <c r="B728" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C728" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>878840744</v>
       </c>
       <c r="B729" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>933222252</v>
       </c>
       <c r="B730" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>818643466</v>
       </c>
       <c r="B731" t="n">
-        <v>13062</v>
+        <v>12564.26</v>
       </c>
       <c r="C731" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>921639451</v>
       </c>
       <c r="B732" t="n">
-        <v>17999</v>
+        <v>22416.48</v>
       </c>
       <c r="C732" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>898595065</v>
       </c>
       <c r="B733" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C733" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>1108673520</v>
       </c>
       <c r="B734" t="n">
-        <v>40281</v>
+        <v>37194.8</v>
       </c>
       <c r="C734" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>1131692660</v>
       </c>
       <c r="B735" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C735" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>922674741</v>
       </c>
       <c r="B736" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C736" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>800163763</v>
       </c>
       <c r="B737" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C737" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>914194829</v>
       </c>
       <c r="B738" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C738" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>855719411</v>
       </c>
       <c r="B739" t="n">
-        <v>205499.5</v>
+        <v>56899.24</v>
       </c>
       <c r="C739" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>617961210</v>
       </c>
       <c r="B740" t="n">
-        <v>40281</v>
+        <v>47047.02</v>
       </c>
       <c r="C740" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>654459237</v>
       </c>
       <c r="B741" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C741" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>881430066</v>
       </c>
       <c r="B742" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C742" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>846719967</v>
       </c>
       <c r="B743" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C743" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>14705584</v>
       </c>
       <c r="B744" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C744" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>1127960842</v>
       </c>
       <c r="B745" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C745" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>929620929</v>
       </c>
       <c r="B746" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C746" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>856070377</v>
       </c>
       <c r="B747" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C747" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>852132910</v>
       </c>
       <c r="B748" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C748" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>15465491</v>
       </c>
       <c r="B749" t="n">
-        <v>17999</v>
+        <v>17490.38</v>
       </c>
       <c r="C749" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>827952466</v>
       </c>
       <c r="B750" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C750" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>1106481473</v>
       </c>
       <c r="B751" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C751" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>863232407</v>
       </c>
       <c r="B752" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C752" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>912637258</v>
       </c>
       <c r="B753" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C753" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>908690837</v>
       </c>
       <c r="B754" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C754" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>900233140</v>
       </c>
       <c r="B755" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C755" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>923737548</v>
       </c>
       <c r="B756" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C756" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>1100897915</v>
       </c>
       <c r="B757" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C757" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>906207929</v>
       </c>
       <c r="B758" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C758" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>935903869</v>
       </c>
       <c r="B759" t="n">
-        <v>25535.5</v>
+        <v>27342.59</v>
       </c>
       <c r="C759" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>878875917</v>
       </c>
       <c r="B760" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C760" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>862601740</v>
       </c>
       <c r="B761" t="n">
-        <v>689000</v>
+        <v>2712.06</v>
       </c>
       <c r="C761" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>902433910</v>
       </c>
       <c r="B762" t="n">
-        <v>25535.5</v>
+        <v>22416.48</v>
       </c>
       <c r="C762" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>1113490438</v>
       </c>
       <c r="B763" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C763" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>880579065</v>
       </c>
       <c r="B764" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C764" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>925710041</v>
       </c>
       <c r="B765" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C765" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>15532531</v>
       </c>
       <c r="B766" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C766" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>858827220</v>
       </c>
       <c r="B767" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C767" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>913003632</v>
       </c>
       <c r="B768" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C768" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>897965539</v>
       </c>
       <c r="B769" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C769" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>672920071</v>
       </c>
       <c r="B770" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C770" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>899548938</v>
       </c>
       <c r="B771" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C771" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>901862882</v>
       </c>
       <c r="B772" t="n">
-        <v>2304.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C772" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>754514742</v>
       </c>
       <c r="B773" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C773" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>1113778256</v>
       </c>
       <c r="B774" t="n">
-        <v>7699</v>
+        <v>7638.16</v>
       </c>
       <c r="C774" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>829164648</v>
       </c>
       <c r="B775" t="n">
-        <v>3149</v>
+        <v>2712.06</v>
       </c>
       <c r="C775" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>877977721</v>
       </c>
       <c r="B776" t="n">
-        <v>4399</v>
+        <v>2712.06</v>
       </c>
       <c r="C776" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>837245504</v>
       </c>
       <c r="B777" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C777" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>872417738</v>
       </c>
       <c r="B778" t="n">
-        <v>1250</v>
+        <v>2712.06</v>
       </c>
       <c r="C778" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>873683289</v>
       </c>
       <c r="B779" t="n">
-        <v>1660.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C779" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>867475577</v>
       </c>
       <c r="B780" t="n">
-        <v>5387.5</v>
+        <v>7638.16</v>
       </c>
       <c r="C780" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>918157396</v>
       </c>
       <c r="B781" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C781" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>1114787972</v>
       </c>
       <c r="B782" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C782" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>1102869667</v>
       </c>
       <c r="B783" t="n">
-        <v>3698</v>
+        <v>2712.06</v>
       </c>
       <c r="C783" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>754170837</v>
       </c>
       <c r="B784" t="n">
-        <v>9812.5</v>
+        <v>12564.26</v>
       </c>
       <c r="C784" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>792344942</v>
       </c>
       <c r="B785" t="n">
-        <v>5387.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C785" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>1131993504</v>
       </c>
       <c r="B786" t="n">
-        <v>2654</v>
+        <v>2712.06</v>
       </c>
       <c r="C786" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>830401802</v>
       </c>
       <c r="B787" t="n">
-        <v>2024.5</v>
+        <v>2712.06</v>
       </c>
       <c r="C787" t="inlineStr">
         <is>
